--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487630_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487630_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0206</v>
+        <v>2.2466</v>
       </c>
       <c r="E2" t="n">
-        <v>9.161099999999999</v>
+        <v>7.6596</v>
       </c>
       <c r="F2" t="n">
-        <v>-5.1405</v>
+        <v>-5.413</v>
       </c>
       <c r="G2" t="n">
         <v>-1.7727</v>
@@ -610,13 +610,13 @@
         <v>1.1642</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5112</v>
+        <v>0.7371</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0771</v>
+        <v>0.5756</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4341</v>
+        <v>0.1615</v>
       </c>
       <c r="V2" t="n">
         <v>2.1179</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4898</v>
+        <v>1.0804</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6363</v>
+        <v>4.336</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.1465</v>
+        <v>-3.2555</v>
       </c>
       <c r="G3" t="n">
         <v>-2.9307</v>
@@ -688,13 +688,13 @@
         <v>1.1642</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1332</v>
+        <v>-0.5426</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3017</v>
+        <v>-0.602</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1685</v>
+        <v>0.0595</v>
       </c>
       <c r="V3" t="n">
         <v>3.3895</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1044</v>
+        <v>0.377</v>
       </c>
       <c r="E4" t="n">
         <v>0.4095</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3051</v>
+        <v>-0.0326</v>
       </c>
       <c r="G4" t="n">
         <v>-0.2241</v>
@@ -766,13 +766,13 @@
         <v>0.3881</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2793</v>
+        <v>0.5518</v>
       </c>
       <c r="T4" t="n">
         <v>0.3645</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0852</v>
+        <v>0.1873</v>
       </c>
       <c r="V4" t="n">
         <v>1.6015</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0502</v>
+        <v>0.1681</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5867</v>
+        <v>4.4866</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.5365</v>
+        <v>-4.3184</v>
       </c>
       <c r="G5" t="n">
         <v>-2.3863</v>
@@ -844,13 +844,13 @@
         <v>0.7761</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3887</v>
+        <v>0.5067</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7413</v>
+        <v>0.6412</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3526</v>
+        <v>-0.1346</v>
       </c>
       <c r="V5" t="n">
         <v>1.2716</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.29</v>
+        <v>-0.8534</v>
       </c>
       <c r="E6" t="n">
-        <v>6.136</v>
+        <v>6.4363</v>
       </c>
       <c r="F6" t="n">
-        <v>-7.4259</v>
+        <v>-7.2897</v>
       </c>
       <c r="G6" t="n">
         <v>2.9721</v>
@@ -922,13 +922,13 @@
         <v>0.7761</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2427</v>
+        <v>-0.8061</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9691</v>
+        <v>-0.6688</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2736</v>
+        <v>-0.1374</v>
       </c>
       <c r="V6" t="n">
         <v>-2.8254</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1881</v>
+        <v>-2.3516</v>
       </c>
       <c r="E7" t="n">
         <v>-0.324</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.8641</v>
+        <v>-2.0276</v>
       </c>
       <c r="G7" t="n">
         <v>-2.9134</v>
@@ -1000,13 +1000,13 @@
         <v>1.3582</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6671</v>
+        <v>0.5036</v>
       </c>
       <c r="T7" t="n">
         <v>0.1346</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5325</v>
+        <v>0.369</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3299</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.5461</v>
+        <v>-4.7542</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0922</v>
+        <v>-1.1913</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.454</v>
+        <v>-3.563</v>
       </c>
       <c r="G8" t="n">
         <v>-2.4994</v>
@@ -1078,13 +1078,13 @@
         <v>0.9702</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5706</v>
+        <v>0.2212</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.775</v>
+        <v>0.1259</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2044</v>
+        <v>0.0954</v>
       </c>
       <c r="V8" t="n">
         <v>-1.506</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.9622</v>
+        <v>-6.5618</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.7708</v>
+        <v>-3.3704</v>
       </c>
       <c r="F9" t="n">
         <v>-3.1914</v>
@@ -1156,10 +1156,10 @@
         <v>0.5821</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5944</v>
+        <v>-0.194</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6662</v>
+        <v>-0.2658</v>
       </c>
       <c r="U9" t="n">
         <v>0.0718</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.4907</v>
+        <v>-8.1632</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5536</v>
+        <v>-2.2533</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.9372</v>
+        <v>-5.9099</v>
       </c>
       <c r="G10" t="n">
         <v>-5.773</v>
@@ -1234,13 +1234,13 @@
         <v>1.5523</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2118</v>
+        <v>0.1158</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4711</v>
+        <v>-0.1708</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2593</v>
+        <v>0.2866</v>
       </c>
       <c r="V10" t="n">
         <v>-2.1179</v>
@@ -1273,7 +1273,7 @@
         <v>16.189</v>
       </c>
       <c r="F11" t="n">
-        <v>-35.0012</v>
+        <v>-35.0011</v>
       </c>
       <c r="G11" t="n">
         <v>-16.7609</v>
@@ -1312,13 +1312,13 @@
         <v>8.7315</v>
       </c>
       <c r="S11" t="n">
-        <v>1.0936</v>
+        <v>1.0935</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1343999999999997</v>
+        <v>0.1344000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9591999999999999</v>
+        <v>0.9591000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2344999999999984</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.7946</v>
+        <v>8.464700000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>9.918200000000001</v>
+        <v>10.3186</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1236</v>
+        <v>-1.8539</v>
       </c>
       <c r="G12" t="n">
         <v>6.2532</v>
@@ -1390,13 +1390,13 @@
         <v>0.9702</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3526</v>
+        <v>-0.6825</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8479</v>
+        <v>-0.4475</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5047</v>
+        <v>-0.2349</v>
       </c>
       <c r="V12" t="n">
         <v>2.1179</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.2063</v>
+        <v>5.2058</v>
       </c>
       <c r="E13" t="n">
-        <v>4.6396</v>
+        <v>3.9389</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5667</v>
+        <v>1.2669</v>
       </c>
       <c r="G13" t="n">
         <v>3.8175</v>
@@ -1468,13 +1468,13 @@
         <v>1.1642</v>
       </c>
       <c r="S13" t="n">
-        <v>1.6306</v>
+        <v>0.6301</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5473</v>
+        <v>-0.1534</v>
       </c>
       <c r="U13" t="n">
-        <v>1.0833</v>
+        <v>0.7835</v>
       </c>
       <c r="V13" t="n">
         <v>0.5642</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B. FERNANDEZ SHEPHARD</t>
+          <t>J. GALLETTO LAMELA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3527</v>
+        <v>3.7837</v>
       </c>
       <c r="E14" t="n">
-        <v>6.7604</v>
+        <v>5.4097</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.4077</v>
+        <v>-1.6259</v>
       </c>
       <c r="G14" t="n">
-        <v>2.2244</v>
+        <v>4.1144</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.0817</v>
+        <v>-0.2167</v>
       </c>
       <c r="I14" t="n">
-        <v>3.3061</v>
+        <v>4.3311</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5784</v>
+        <v>6.637</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1277</v>
+        <v>1.6107</v>
       </c>
       <c r="L14" t="n">
-        <v>3.4507</v>
+        <v>5.0263</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.3541</v>
+        <v>-2.5225</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2095</v>
+        <v>-1.8274</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1446</v>
+        <v>-0.6952</v>
       </c>
       <c r="P14" t="n">
-        <v>1.3582</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3582</v>
+        <v>1.5523</v>
       </c>
       <c r="S14" t="n">
-        <v>0.382</v>
+        <v>-0.4307</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1222</v>
+        <v>-0.387</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2598</v>
+        <v>-0.0437</v>
       </c>
       <c r="V14" t="n">
+        <v>1.4582</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.0701</v>
+      </c>
+      <c r="X14" t="n">
         <v>-0.6119</v>
-      </c>
-      <c r="W14" t="n">
-        <v>3.0597</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-3.6716</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. GALLETTO LAMELA</t>
+          <t>B. FERNANDEZ SHEPHARD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1108</v>
+        <v>3.2342</v>
       </c>
       <c r="E15" t="n">
-        <v>5.0093</v>
+        <v>6.5602</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.8985</v>
+        <v>-3.3259</v>
       </c>
       <c r="G15" t="n">
-        <v>4.1144</v>
+        <v>2.2244</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2167</v>
+        <v>-1.0817</v>
       </c>
       <c r="I15" t="n">
-        <v>4.3311</v>
+        <v>3.3061</v>
       </c>
       <c r="J15" t="n">
-        <v>6.637</v>
+        <v>3.5784</v>
       </c>
       <c r="K15" t="n">
-        <v>1.6107</v>
+        <v>0.1277</v>
       </c>
       <c r="L15" t="n">
-        <v>5.0263</v>
+        <v>3.4507</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.5225</v>
+        <v>-1.3541</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.8274</v>
+        <v>-1.2095</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6952</v>
+        <v>-0.1446</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.3582</v>
+        <v>1.3582</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9105</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5523</v>
+        <v>1.3582</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1036</v>
+        <v>0.2636</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7874</v>
+        <v>-0.078</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3163</v>
+        <v>0.3415</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4582</v>
+        <v>-0.6119</v>
       </c>
       <c r="W15" t="n">
-        <v>2.0701</v>
+        <v>3.0597</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6119</v>
+        <v>-3.6716</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6469</v>
+        <v>2.436</v>
       </c>
       <c r="E16" t="n">
-        <v>3.6211</v>
+        <v>4.522</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9742</v>
+        <v>-2.086</v>
       </c>
       <c r="G16" t="n">
         <v>-0.7175</v>
@@ -1702,13 +1702,13 @@
         <v>1.3582</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9654</v>
+        <v>-0.1764</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1508</v>
+        <v>-0.2499</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1853</v>
+        <v>0.0735</v>
       </c>
       <c r="V16" t="n">
         <v>2.1657</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. KHIVRENKO</t>
+          <t>K. RIVEROL DE LAS CASAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6682</v>
+        <v>1.2698</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4669</v>
+        <v>2.3801</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2012</v>
+        <v>-1.1103</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.472</v>
+        <v>0.8657</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4548</v>
+        <v>-2.1141</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0172</v>
+        <v>2.9797</v>
       </c>
       <c r="J17" t="n">
-        <v>0.163</v>
+        <v>3.1328</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0412</v>
+        <v>-0.6756</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1218</v>
+        <v>3.8084</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.635</v>
+        <v>-2.2672</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.496</v>
+        <v>-1.4385</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.139</v>
+        <v>-0.8286</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9702</v>
+        <v>1.7463</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.194</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9702</v>
+        <v>1.9403</v>
       </c>
       <c r="S17" t="n">
-        <v>0.17</v>
+        <v>-0.1183</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3039</v>
+        <v>-0.2288</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1339</v>
+        <v>0.1105</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.3299</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. RIVEROL DE LAS CASAS</t>
+          <t>M. KHIVRENKO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2537</v>
+        <v>0.4134</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5793</v>
+        <v>0.2667</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3256</v>
+        <v>0.1467</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8657</v>
+        <v>-0.472</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.1141</v>
+        <v>-0.4548</v>
       </c>
       <c r="I18" t="n">
-        <v>2.9797</v>
+        <v>-0.0172</v>
       </c>
       <c r="J18" t="n">
-        <v>3.1328</v>
+        <v>0.163</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6756</v>
+        <v>0.0412</v>
       </c>
       <c r="L18" t="n">
-        <v>3.8084</v>
+        <v>0.1218</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.2672</v>
+        <v>-0.635</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.4385</v>
+        <v>-0.496</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8286</v>
+        <v>-0.139</v>
       </c>
       <c r="P18" t="n">
-        <v>1.7463</v>
+        <v>0.9702</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.194</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9403</v>
+        <v>0.9702</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1343</v>
+        <v>-0.0847</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0296</v>
+        <v>0.1037</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1047</v>
+        <v>-0.1884</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3299</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.894</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0624</v>
+        <v>-1.0929</v>
       </c>
       <c r="E19" t="n">
-        <v>2.8066</v>
+        <v>2.5063</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.869</v>
+        <v>-3.5992</v>
       </c>
       <c r="G19" t="n">
         <v>1.0308</v>
@@ -1936,13 +1936,13 @@
         <v>1.5523</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0426</v>
+        <v>0.0121</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5473</v>
+        <v>0.247</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5047</v>
+        <v>-0.2349</v>
       </c>
       <c r="V19" t="n">
         <v>-1.5537</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. MANERO GUZMAN</t>
+          <t>P. HERNANDEZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3165</v>
+        <v>-2.1151</v>
       </c>
       <c r="E20" t="n">
-        <v>2.1183</v>
+        <v>-2.2187</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.4348</v>
+        <v>0.1037</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1312</v>
+        <v>-0.4868</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2241</v>
+        <v>-0.9161</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0929</v>
+        <v>0.4293</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4622</v>
+        <v>-0.4637</v>
       </c>
       <c r="K20" t="n">
-        <v>1.277</v>
+        <v>-0.6261</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1852</v>
+        <v>0.1624</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.331</v>
+        <v>-0.0231</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0529</v>
+        <v>-0.29</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2781</v>
+        <v>0.2669</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3881</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.194</v>
+        <v>-1.9403</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5821</v>
+        <v>0.194</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5641</v>
+        <v>0.4001</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8501</v>
+        <v>0.1853</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.286</v>
+        <v>0.2148</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.4</v>
+        <v>-0.2821</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.4</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. HERNANDEZ RODRIGUEZ</t>
+          <t>S. MANERO GUZMAN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.842</v>
+        <v>-2.1201</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9184</v>
+        <v>1.3175</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0764</v>
+        <v>-3.4377</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4868</v>
+        <v>0.1312</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9161</v>
+        <v>0.2241</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4293</v>
+        <v>-0.0929</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4637</v>
+        <v>1.4622</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6261</v>
+        <v>1.277</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1624</v>
+        <v>0.1852</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0231</v>
+        <v>-1.331</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.29</v>
+        <v>-1.0529</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2669</v>
+        <v>-0.2781</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.7463</v>
+        <v>0.3881</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9403</v>
+        <v>-0.194</v>
       </c>
       <c r="R21" t="n">
-        <v>0.194</v>
+        <v>0.5821</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6732</v>
+        <v>-0.2395</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4856</v>
+        <v>0.0493</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1875</v>
+        <v>-0.2888</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2821</v>
+        <v>-2.4</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2821</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>18.8123</v>
+        <v>19.4795</v>
       </c>
       <c r="E22" t="n">
-        <v>35.0013</v>
+        <v>35.00130000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-16.1891</v>
+        <v>-15.5216</v>
       </c>
       <c r="G22" t="n">
         <v>16.7609</v>
@@ -2158,28 +2158,28 @@
         <v>-11.7322</v>
       </c>
       <c r="O22" t="n">
-        <v>-4.1989</v>
+        <v>-4.198899999999999</v>
       </c>
       <c r="P22" t="n">
         <v>2.9105</v>
       </c>
       <c r="Q22" t="n">
-        <v>-8.731399999999999</v>
+        <v>-8.731400000000001</v>
       </c>
       <c r="R22" t="n">
         <v>11.642</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0934</v>
+        <v>-0.4262</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9593</v>
+        <v>-0.9593000000000002</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1344000000000002</v>
+        <v>0.5330999999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2344000000000002</v>
+        <v>0.2344000000000004</v>
       </c>
       <c r="W22" t="n">
         <v>11.9998</v>
